--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.912785020072662</v>
+        <v>1.285827565761808</v>
       </c>
       <c r="D2" t="n">
-        <v>7.998592042790633</v>
+        <v>1.299771206953478</v>
       </c>
       <c r="E2" t="n">
-        <v>8.720323946902429</v>
+        <v>1.417052641371645</v>
       </c>
       <c r="F2" t="n">
-        <v>8.702434561961924</v>
+        <v>1.414145616318812</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.904368343790162</v>
+        <v>1.446959855865901</v>
       </c>
       <c r="D3" t="n">
-        <v>8.802828097207518</v>
+        <v>1.430459565796222</v>
       </c>
       <c r="E3" t="n">
-        <v>8.720323946902429</v>
+        <v>1.417052641371645</v>
       </c>
       <c r="F3" t="n">
-        <v>8.702434561961924</v>
+        <v>1.414145616318812</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7.838173920788468</v>
+        <v>1.273703262128126</v>
       </c>
       <c r="D4" t="n">
-        <v>7.806575235184993</v>
+        <v>1.268568475717561</v>
       </c>
       <c r="E4" t="n">
-        <v>8.720323946902429</v>
+        <v>1.417052641371645</v>
       </c>
       <c r="F4" t="n">
-        <v>8.702434561961924</v>
+        <v>1.414145616318812</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.33369945715344</v>
+        <v>4.604226161787434</v>
       </c>
       <c r="D5" t="n">
-        <v>28.28153430318004</v>
+        <v>4.595749324266756</v>
       </c>
       <c r="E5" t="n">
-        <v>8.720323946902429</v>
+        <v>1.417052641371645</v>
       </c>
       <c r="F5" t="n">
-        <v>8.702434561961924</v>
+        <v>1.414145616318812</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
